--- a/preorder_forms/033_school_visit_pre_order_form--preorder_forms.xlsx
+++ b/preorder_forms/033_school_visit_pre_order_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
+          <t>Student Attendance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,20 +548,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>school_visit_pre_order</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Number of People Attending</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter a number greater than 1</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,20 +575,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Date of Visit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +602,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Time of Visit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HH -MM</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +629,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
+          <t>Students Attending with Chaperone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +652,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
+          <t>Contact Method</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +675,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
+          <t>Grade Level</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,10 +698,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Medical Conditions</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe any medical conditions that may impact the student's ability to participate in the visit</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -709,10 +725,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide any other relevant information</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,7 +742,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,10 +752,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Student's Birthday</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -755,13 +779,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Special Accommodations</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please describe any special accommodations that the student may need</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>school_visit_pre_order_form_page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -776,12 +827,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -838,7 +889,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form_page_3_choices</t>
+          <t>school_visit_pre_order_form_page_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,7 +906,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form_page_3_choices</t>
+          <t>school_visit_pre_order_form_page_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -872,34 +923,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form_page_4_choices</t>
+          <t>school_visit_pre_order_form_page_7_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pre-k-5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pre-K-5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>school_visit_pre_order_form_page_4_choices</t>
+          <t>school_visit_pre_order_form_page_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>6-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>school_visit_pre_order_form_page_7_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9-12</t>
         </is>
       </c>
     </row>
